--- a/templates/blank.xlsx
+++ b/templates/blank.xlsx
@@ -24,7 +24,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Christian Sans"/>
+      <name val="Novus Serif"/>
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
@@ -119,8 +119,8 @@
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Christian Sans"/>
-        <a:font script="Hebr" typeface="Christian Sans"/>
+        <a:font script="Arab" typeface="Novus Serif"/>
+        <a:font script="Hebr" typeface="Novus Serif"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
@@ -142,20 +142,20 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Christian Sans"/>
+        <a:font script="Viet" typeface="Novus Serif"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Christian Sans" panose="020F0502020204030204"/>
+        <a:latin typeface="Novus Serif" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Christian Sans"/>
-        <a:font script="Hebr" typeface="Christian Sans"/>
+        <a:font script="Arab" typeface="Novus Serif"/>
+        <a:font script="Hebr" typeface="Novus Serif"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
@@ -177,7 +177,7 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Christian Sans"/>
+        <a:font script="Viet" typeface="Novus Serif"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>

--- a/templates/blank.xlsx
+++ b/templates/blank.xlsx
@@ -24,7 +24,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Novus Serif"/>
+      <name val="Asteria Serif"/>
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
@@ -119,8 +119,8 @@
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Novus Serif"/>
-        <a:font script="Hebr" typeface="Novus Serif"/>
+        <a:font script="Arab" typeface="Asteria Serif"/>
+        <a:font script="Hebr" typeface="Asteria Serif"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
@@ -142,20 +142,20 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Novus Serif"/>
+        <a:font script="Viet" typeface="Asteria Serif"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Novus Serif" panose="020F0502020204030204"/>
+        <a:latin typeface="Asteria Serif" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Novus Serif"/>
-        <a:font script="Hebr" typeface="Novus Serif"/>
+        <a:font script="Arab" typeface="Asteria Serif"/>
+        <a:font script="Hebr" typeface="Asteria Serif"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
@@ -177,7 +177,7 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Novus Serif"/>
+        <a:font script="Viet" typeface="Asteria Serif"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
